--- a/bioinfo_revision/simulation_results/tables/mrggi/by_sample_size/mrggi_truth_n670.xlsx
+++ b/bioinfo_revision/simulation_results/tables/mrggi/by_sample_size/mrggi_truth_n670.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -405,25 +405,25 @@
         </is>
       </c>
       <c r="B2">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D2">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="H2">
-        <v>0.375</v>
+        <v>0.1558441558441558</v>
       </c>
     </row>
     <row r="3">
@@ -436,22 +436,22 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
+        <v>30</v>
+      </c>
+      <c r="F3">
         <v>48</v>
       </c>
-      <c r="F3">
-        <v>49</v>
-      </c>
       <c r="G3">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="H3">
-        <v>0.6065573770491803</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="4">
@@ -482,51 +482,76 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Screened out</t>
         </is>
       </c>
       <c r="B5">
+        <v>33</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>18</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
         <v>60</v>
-      </c>
-      <c r="C5">
-        <v>60</v>
-      </c>
-      <c r="D5">
-        <v>60</v>
-      </c>
-      <c r="E5">
-        <v>60</v>
-      </c>
-      <c r="F5">
-        <v>60</v>
-      </c>
-      <c r="G5">
-        <v>300</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>60</v>
+      </c>
+      <c r="D6">
+        <v>60</v>
+      </c>
+      <c r="E6">
+        <v>60</v>
+      </c>
+      <c r="F6">
+        <v>60</v>
+      </c>
+      <c r="G6">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="B6">
-        <v>0.75</v>
-      </c>
-      <c r="C6">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="D6">
+      <c r="B7">
+        <v>0.2</v>
+      </c>
+      <c r="C7">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="D7">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="E7">
         <v>0</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0.8166666666666667</v>
-      </c>
-      <c r="H6">
-        <v>0.3966666666666667</v>
+      <c r="F7">
+        <v>0.8</v>
+      </c>
+      <c r="H7">
+        <v>0.29</v>
       </c>
     </row>
   </sheetData>
@@ -536,7 +561,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -573,16 +598,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C2">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D2">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="E2">
-        <v>0.375</v>
+        <v>0.1558441558441558</v>
       </c>
     </row>
     <row r="3">
@@ -592,16 +617,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C3">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="E3">
-        <v>0.6065573770491803</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="4">
@@ -623,33 +648,49 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Screened out</t>
         </is>
       </c>
       <c r="B5">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="C5">
-        <v>180</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>300</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>120</v>
+      </c>
+      <c r="C6">
+        <v>180</v>
+      </c>
+      <c r="D6">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="B6">
-        <v>0.375</v>
-      </c>
-      <c r="C6">
-        <v>0.4111111111111111</v>
-      </c>
-      <c r="E6">
-        <v>0.3966666666666667</v>
+      <c r="B7">
+        <v>0.1</v>
+      </c>
+      <c r="C7">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="E7">
+        <v>0.29</v>
       </c>
     </row>
   </sheetData>
@@ -778,7 +819,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 15:19:19</t>
+          <t>2026-08-27 19:53:39</t>
         </is>
       </c>
     </row>

--- a/bioinfo_revision/simulation_results/tables/mrggi/by_sample_size/mrggi_truth_n670.xlsx
+++ b/bioinfo_revision/simulation_results/tables/mrggi/by_sample_size/mrggi_truth_n670.xlsx
@@ -7,9 +7,10 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="edge_pred_x_model_true" sheetId="1" r:id="rId1"/>
-    <sheet name="edge_pred_x_edge_true" sheetId="2" r:id="rId2"/>
-    <sheet name="info" sheetId="3" r:id="rId3"/>
+    <sheet name="model_pred_x_model_true" sheetId="1" r:id="rId1"/>
+    <sheet name="edge_pred_x_model_true" sheetId="2" r:id="rId2"/>
+    <sheet name="edge_pred_x_edge_true" sheetId="3" r:id="rId3"/>
+    <sheet name="info" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -353,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -401,157 +402,213 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T1 - T2 Edge Absent</t>
+          <t>M0</t>
         </is>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="H2">
-        <v>0.1558441558441558</v>
+        <v>0.4545454545454545</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T1 - T2 Edge Present</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="H3">
-        <v>0.7142857142857143</v>
+        <v>0.6888888888888889</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Weak instrument</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Screened out</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="B5">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>2</v>
       </c>
-      <c r="G5">
-        <v>60</v>
+      <c r="H5">
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="B6">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F6">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="G6">
-        <v>300</v>
+        <v>98</v>
+      </c>
+      <c r="H6">
+        <v>0.4387755102040816</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>54</v>
+      </c>
+      <c r="C7">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>55</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>60</v>
+      </c>
+      <c r="C8">
+        <v>60</v>
+      </c>
+      <c r="D8">
+        <v>60</v>
+      </c>
+      <c r="E8">
+        <v>60</v>
+      </c>
+      <c r="F8">
+        <v>60</v>
+      </c>
+      <c r="G8">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="B7">
-        <v>0.2</v>
-      </c>
-      <c r="C7">
-        <v>0.4333333333333333</v>
-      </c>
-      <c r="D7">
+      <c r="B9">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="C9">
+        <v>0.5166666666666667</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <v>0.01666666666666667</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0.8</v>
-      </c>
-      <c r="H7">
-        <v>0.29</v>
+      <c r="F9">
+        <v>0.7166666666666667</v>
+      </c>
+      <c r="H9">
+        <v>0.2666666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -561,7 +618,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -572,20 +629,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>T1 - T2 Edge Absent</t>
+          <t>M0</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>T1 - T2 Edge Present</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
@@ -601,12 +673,21 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="D2">
+        <v>49</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>77</v>
       </c>
-      <c r="E2">
+      <c r="H2">
         <v>0.1558441558441558</v>
       </c>
     </row>
@@ -617,15 +698,24 @@
         </is>
       </c>
       <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>26</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>30</v>
       </c>
-      <c r="C3">
-        <v>75</v>
-      </c>
-      <c r="D3">
+      <c r="F3">
+        <v>48</v>
+      </c>
+      <c r="G3">
         <v>105</v>
       </c>
-      <c r="E3">
+      <c r="H3">
         <v>0.7142857142857143</v>
       </c>
     </row>
@@ -636,12 +726,21 @@
         </is>
       </c>
       <c r="B4">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D4">
+        <v>7</v>
+      </c>
+      <c r="E4">
+        <v>12</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4">
         <v>58</v>
       </c>
     </row>
@@ -652,12 +751,21 @@
         </is>
       </c>
       <c r="B5">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>18</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
         <v>60</v>
       </c>
     </row>
@@ -668,12 +776,21 @@
         </is>
       </c>
       <c r="B6">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="C6">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="D6">
+        <v>60</v>
+      </c>
+      <c r="E6">
+        <v>60</v>
+      </c>
+      <c r="F6">
+        <v>60</v>
+      </c>
+      <c r="G6">
         <v>300</v>
       </c>
     </row>
@@ -684,12 +801,21 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C7">
-        <v>0.4166666666666667</v>
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="D7">
+        <v>0.01666666666666667</v>
       </c>
       <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0.8</v>
+      </c>
+      <c r="H7">
         <v>0.29</v>
       </c>
     </row>
@@ -700,6 +826,145 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>inferred</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>T1 - T2 Edge Absent</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>T1 - T2 Edge Present</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>T1 - T2 Edge Absent</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>65</v>
+      </c>
+      <c r="D2">
+        <v>77</v>
+      </c>
+      <c r="E2">
+        <v>0.1558441558441558</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T1 - T2 Edge Present</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>30</v>
+      </c>
+      <c r="C3">
+        <v>75</v>
+      </c>
+      <c r="D3">
+        <v>105</v>
+      </c>
+      <c r="E3">
+        <v>0.7142857142857143</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Weak instrument</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>27</v>
+      </c>
+      <c r="C4">
+        <v>31</v>
+      </c>
+      <c r="D4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Screened out</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>51</v>
+      </c>
+      <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>120</v>
+      </c>
+      <c r="C6">
+        <v>180</v>
+      </c>
+      <c r="D6">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.1</v>
+      </c>
+      <c r="C7">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="E7">
+        <v>0.29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -783,7 +1048,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>none -- see below</t>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -807,7 +1072,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no -- MR-GGI does not return a model call, so it cannot be cross-tabulated against the generating model</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,7 +1084,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 19:53:39</t>
+          <t>2026-08-27 23:10:27</t>
         </is>
       </c>
     </row>
